--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124620142</v>
+        <v>124621255</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481241</v>
+        <v>481309</v>
       </c>
       <c r="R2" t="n">
-        <v>6860052</v>
+        <v>6859892</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124620046</v>
+        <v>124621053</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -810,29 +810,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481239</v>
+        <v>481346</v>
       </c>
       <c r="R3" t="n">
-        <v>6860075</v>
+        <v>6859891</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -990,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124621255</v>
+        <v>124620675</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1023,20 +1014,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481309</v>
+        <v>481300</v>
       </c>
       <c r="R5" t="n">
-        <v>6859892</v>
+        <v>6859946</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620675</v>
+        <v>124620046</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481300</v>
+        <v>481239</v>
       </c>
       <c r="R6" t="n">
-        <v>6859946</v>
+        <v>6860075</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124621053</v>
+        <v>124620142</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481346</v>
+        <v>481241</v>
       </c>
       <c r="R7" t="n">
-        <v>6859891</v>
+        <v>6860052</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124621255</v>
+        <v>124620675</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,20 +708,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481309</v>
+        <v>481300</v>
       </c>
       <c r="R2" t="n">
-        <v>6859892</v>
+        <v>6859946</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124621053</v>
+        <v>124621255</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481346</v>
+        <v>481309</v>
       </c>
       <c r="R3" t="n">
-        <v>6859891</v>
+        <v>6859892</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124620934</v>
+        <v>124621053</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481353</v>
+        <v>481346</v>
       </c>
       <c r="R4" t="n">
-        <v>6859911</v>
+        <v>6859891</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124620675</v>
+        <v>124620934</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1014,26 +1023,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481300</v>
+        <v>481353</v>
       </c>
       <c r="R5" t="n">
-        <v>6859946</v>
+        <v>6859911</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620046</v>
+        <v>124620142</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,50 +1104,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481239</v>
+        <v>481241</v>
       </c>
       <c r="R6" t="n">
-        <v>6860075</v>
+        <v>6860052</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620142</v>
+        <v>124620046</v>
       </c>
       <c r="B7" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,41 +1206,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481241</v>
+        <v>481239</v>
       </c>
       <c r="R7" t="n">
-        <v>6860052</v>
+        <v>6860075</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124621255</v>
+        <v>124620934</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481309</v>
+        <v>481353</v>
       </c>
       <c r="R3" t="n">
-        <v>6859892</v>
+        <v>6859911</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124621053</v>
+        <v>124621255</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481346</v>
+        <v>481309</v>
       </c>
       <c r="R4" t="n">
-        <v>6859891</v>
+        <v>6859892</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124620934</v>
+        <v>124620597</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481353</v>
+        <v>481297</v>
       </c>
       <c r="R5" t="n">
-        <v>6859911</v>
+        <v>6859950</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620142</v>
+        <v>124621053</v>
       </c>
       <c r="B6" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481241</v>
+        <v>481346</v>
       </c>
       <c r="R6" t="n">
-        <v>6860052</v>
+        <v>6859891</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620046</v>
+        <v>124620142</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,50 +1206,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481239</v>
+        <v>481241</v>
       </c>
       <c r="R7" t="n">
-        <v>6860075</v>
+        <v>6860052</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124620597</v>
+        <v>124620046</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1338,17 +1329,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481297</v>
+        <v>481239</v>
       </c>
       <c r="R8" t="n">
-        <v>6859950</v>
+        <v>6860075</v>
       </c>
       <c r="S8" t="n">
         <v>12</v>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124621255</v>
+        <v>124620597</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481309</v>
+        <v>481297</v>
       </c>
       <c r="R4" t="n">
-        <v>6859892</v>
+        <v>6859950</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124620597</v>
+        <v>124621053</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481297</v>
+        <v>481346</v>
       </c>
       <c r="R5" t="n">
-        <v>6859950</v>
+        <v>6859891</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124621053</v>
+        <v>124620046</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1125,20 +1125,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481346</v>
+        <v>481239</v>
       </c>
       <c r="R6" t="n">
-        <v>6859891</v>
+        <v>6860075</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620142</v>
+        <v>124621255</v>
       </c>
       <c r="B7" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,13 +1243,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481241</v>
+        <v>481309</v>
       </c>
       <c r="R7" t="n">
-        <v>6860052</v>
+        <v>6859892</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124620046</v>
+        <v>124620142</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,50 +1317,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481239</v>
+        <v>481241</v>
       </c>
       <c r="R8" t="n">
-        <v>6860075</v>
+        <v>6860052</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,6 +1404,228 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124825237</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kropptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>481198</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6859917</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124825238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kropptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>481211</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6859812</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124620675</v>
+        <v>124620046</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481300</v>
+        <v>481239</v>
       </c>
       <c r="R2" t="n">
-        <v>6859946</v>
+        <v>6860075</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124620934</v>
+        <v>124620142</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481353</v>
+        <v>481241</v>
       </c>
       <c r="R3" t="n">
-        <v>6859911</v>
+        <v>6860052</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124620597</v>
+        <v>124621255</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481297</v>
+        <v>481309</v>
       </c>
       <c r="R4" t="n">
-        <v>6859950</v>
+        <v>6859892</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124621053</v>
+        <v>124620597</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481346</v>
+        <v>481297</v>
       </c>
       <c r="R5" t="n">
-        <v>6859891</v>
+        <v>6859950</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620046</v>
+        <v>124621053</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1125,29 +1125,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481239</v>
+        <v>481346</v>
       </c>
       <c r="R6" t="n">
-        <v>6860075</v>
+        <v>6859891</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124621255</v>
+        <v>124620675</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1236,20 +1227,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481309</v>
+        <v>481300</v>
       </c>
       <c r="R7" t="n">
-        <v>6859892</v>
+        <v>6859946</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124620142</v>
+        <v>124620934</v>
       </c>
       <c r="B8" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481241</v>
+        <v>481353</v>
       </c>
       <c r="R8" t="n">
-        <v>6860052</v>
+        <v>6859911</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124620597</v>
+        <v>124621053</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481297</v>
+        <v>481346</v>
       </c>
       <c r="R5" t="n">
-        <v>6859950</v>
+        <v>6859891</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124621053</v>
+        <v>124620597</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481346</v>
+        <v>481297</v>
       </c>
       <c r="R6" t="n">
-        <v>6859891</v>
+        <v>6859950</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124621053</v>
+        <v>124620597</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481346</v>
+        <v>481297</v>
       </c>
       <c r="R5" t="n">
-        <v>6859891</v>
+        <v>6859950</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620597</v>
+        <v>124621053</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481297</v>
+        <v>481346</v>
       </c>
       <c r="R6" t="n">
-        <v>6859950</v>
+        <v>6859891</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124620046</v>
+        <v>124621053</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,29 +708,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481239</v>
+        <v>481346</v>
       </c>
       <c r="R2" t="n">
-        <v>6860075</v>
+        <v>6859891</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124620142</v>
+        <v>124620675</v>
       </c>
       <c r="B3" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,41 +789,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481241</v>
+        <v>481300</v>
       </c>
       <c r="R3" t="n">
-        <v>6860052</v>
+        <v>6859946</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124620597</v>
+        <v>124620046</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1023,17 +1023,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481297</v>
+        <v>481239</v>
       </c>
       <c r="R5" t="n">
-        <v>6859950</v>
+        <v>6860075</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
@@ -1092,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124621053</v>
+        <v>124620142</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,13 +1141,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481346</v>
+        <v>481241</v>
       </c>
       <c r="R6" t="n">
-        <v>6859891</v>
+        <v>6860052</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620675</v>
+        <v>124620934</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1227,26 +1236,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481300</v>
+        <v>481353</v>
       </c>
       <c r="R7" t="n">
-        <v>6859946</v>
+        <v>6859911</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124620934</v>
+        <v>124620597</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481353</v>
+        <v>481297</v>
       </c>
       <c r="R8" t="n">
-        <v>6859911</v>
+        <v>6859950</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124621053</v>
+        <v>124621255</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481346</v>
+        <v>481309</v>
       </c>
       <c r="R2" t="n">
-        <v>6859891</v>
+        <v>6859892</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124620675</v>
+        <v>124620142</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,50 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481300</v>
+        <v>481241</v>
       </c>
       <c r="R3" t="n">
-        <v>6859946</v>
+        <v>6860052</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124621255</v>
+        <v>124621053</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -928,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481309</v>
+        <v>481346</v>
       </c>
       <c r="R4" t="n">
-        <v>6859892</v>
+        <v>6859891</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124620046</v>
+        <v>124620597</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1023,26 +1014,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481239</v>
+        <v>481297</v>
       </c>
       <c r="R5" t="n">
-        <v>6860075</v>
+        <v>6859950</v>
       </c>
       <c r="S5" t="n">
         <v>12</v>
@@ -1101,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620142</v>
+        <v>124620046</v>
       </c>
       <c r="B6" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,41 +1095,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481241</v>
+        <v>481239</v>
       </c>
       <c r="R6" t="n">
-        <v>6860052</v>
+        <v>6860075</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620934</v>
+        <v>124620675</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1236,17 +1227,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481353</v>
+        <v>481300</v>
       </c>
       <c r="R7" t="n">
-        <v>6859911</v>
+        <v>6859946</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124620597</v>
+        <v>124620934</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481297</v>
+        <v>481353</v>
       </c>
       <c r="R8" t="n">
-        <v>6859950</v>
+        <v>6859911</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124621255</v>
+        <v>124620675</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,20 +708,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481309</v>
+        <v>481300</v>
       </c>
       <c r="R2" t="n">
-        <v>6859892</v>
+        <v>6859946</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124620142</v>
+        <v>124620934</v>
       </c>
       <c r="B3" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481241</v>
+        <v>481353</v>
       </c>
       <c r="R3" t="n">
-        <v>6860052</v>
+        <v>6859911</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124621053</v>
+        <v>124620142</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481346</v>
+        <v>481241</v>
       </c>
       <c r="R4" t="n">
-        <v>6859891</v>
+        <v>6860052</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124620597</v>
+        <v>124621053</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1021,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481297</v>
+        <v>481346</v>
       </c>
       <c r="R5" t="n">
-        <v>6859950</v>
+        <v>6859891</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620046</v>
+        <v>124621255</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1116,29 +1125,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481239</v>
+        <v>481309</v>
       </c>
       <c r="R6" t="n">
-        <v>6860075</v>
+        <v>6859892</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620675</v>
+        <v>124620597</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1227,29 +1227,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481300</v>
+        <v>481297</v>
       </c>
       <c r="R7" t="n">
-        <v>6859946</v>
+        <v>6859950</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124620934</v>
+        <v>124620046</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1338,20 +1329,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481353</v>
+        <v>481239</v>
       </c>
       <c r="R8" t="n">
-        <v>6859911</v>
+        <v>6860075</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124620675</v>
+        <v>124620934</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,26 +708,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481300</v>
+        <v>481353</v>
       </c>
       <c r="R2" t="n">
-        <v>6859946</v>
+        <v>6859911</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124620934</v>
+        <v>124620142</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481353</v>
+        <v>481241</v>
       </c>
       <c r="R3" t="n">
-        <v>6859911</v>
+        <v>6860052</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124620142</v>
+        <v>124621053</v>
       </c>
       <c r="B4" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481241</v>
+        <v>481346</v>
       </c>
       <c r="R4" t="n">
-        <v>6860052</v>
+        <v>6859891</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124621053</v>
+        <v>124621255</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1030,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481346</v>
+        <v>481309</v>
       </c>
       <c r="R5" t="n">
-        <v>6859891</v>
+        <v>6859892</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124621255</v>
+        <v>124620597</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1132,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481309</v>
+        <v>481297</v>
       </c>
       <c r="R6" t="n">
-        <v>6859892</v>
+        <v>6859950</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620597</v>
+        <v>124620046</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1227,17 +1218,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481297</v>
+        <v>481239</v>
       </c>
       <c r="R7" t="n">
-        <v>6859950</v>
+        <v>6860075</v>
       </c>
       <c r="S7" t="n">
         <v>12</v>
@@ -1296,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124620046</v>
+        <v>124620675</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481239</v>
+        <v>481300</v>
       </c>
       <c r="R8" t="n">
-        <v>6860075</v>
+        <v>6859946</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124825237</v>
+        <v>124825238</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1451,13 +1451,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481198</v>
+        <v>481211</v>
       </c>
       <c r="R9" t="n">
-        <v>6859917</v>
+        <v>6859812</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1518,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124825238</v>
+        <v>124825237</v>
       </c>
       <c r="B10" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481211</v>
+        <v>481198</v>
       </c>
       <c r="R10" t="n">
-        <v>6859812</v>
+        <v>6859917</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124620934</v>
+        <v>124621255</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481353</v>
+        <v>481309</v>
       </c>
       <c r="R2" t="n">
-        <v>6859911</v>
+        <v>6859892</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124620142</v>
+        <v>124620046</v>
       </c>
       <c r="B3" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481241</v>
+        <v>481239</v>
       </c>
       <c r="R3" t="n">
-        <v>6860052</v>
+        <v>6860075</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124621053</v>
+        <v>124620597</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481346</v>
+        <v>481297</v>
       </c>
       <c r="R4" t="n">
-        <v>6859891</v>
+        <v>6859950</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124621255</v>
+        <v>124620142</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481309</v>
+        <v>481241</v>
       </c>
       <c r="R5" t="n">
-        <v>6859892</v>
+        <v>6860052</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620597</v>
+        <v>124620934</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1123,13 +1132,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481297</v>
+        <v>481353</v>
       </c>
       <c r="R6" t="n">
-        <v>6859950</v>
+        <v>6859911</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620046</v>
+        <v>124621053</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1218,29 +1227,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481239</v>
+        <v>481346</v>
       </c>
       <c r="R7" t="n">
-        <v>6860075</v>
+        <v>6859891</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124621255</v>
+        <v>124620046</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,20 +708,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481309</v>
+        <v>481239</v>
       </c>
       <c r="R2" t="n">
-        <v>6859892</v>
+        <v>6860075</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124620046</v>
+        <v>124620597</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -810,26 +819,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481239</v>
+        <v>481297</v>
       </c>
       <c r="R3" t="n">
-        <v>6860075</v>
+        <v>6859950</v>
       </c>
       <c r="S3" t="n">
         <v>12</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124620597</v>
+        <v>124620142</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481297</v>
+        <v>481241</v>
       </c>
       <c r="R4" t="n">
-        <v>6859950</v>
+        <v>6860052</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124620142</v>
+        <v>124621053</v>
       </c>
       <c r="B5" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481241</v>
+        <v>481346</v>
       </c>
       <c r="R5" t="n">
-        <v>6860052</v>
+        <v>6859891</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620934</v>
+        <v>124620675</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1125,17 +1125,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481353</v>
+        <v>481300</v>
       </c>
       <c r="R6" t="n">
-        <v>6859911</v>
+        <v>6859946</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124621053</v>
+        <v>124620934</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1234,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481346</v>
+        <v>481353</v>
       </c>
       <c r="R7" t="n">
-        <v>6859891</v>
+        <v>6859911</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124620675</v>
+        <v>124621255</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1329,29 +1338,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481300</v>
+        <v>481309</v>
       </c>
       <c r="R8" t="n">
-        <v>6859946</v>
+        <v>6859892</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124620046</v>
+        <v>124621053</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,29 +708,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481239</v>
+        <v>481346</v>
       </c>
       <c r="R2" t="n">
-        <v>6860075</v>
+        <v>6859891</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124620597</v>
+        <v>124621255</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -826,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481297</v>
+        <v>481309</v>
       </c>
       <c r="R3" t="n">
-        <v>6859950</v>
+        <v>6859892</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124620142</v>
+        <v>124620934</v>
       </c>
       <c r="B4" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481241</v>
+        <v>481353</v>
       </c>
       <c r="R4" t="n">
-        <v>6860052</v>
+        <v>6859911</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124621053</v>
+        <v>124620675</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1023,17 +1014,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481346</v>
+        <v>481300</v>
       </c>
       <c r="R5" t="n">
-        <v>6859891</v>
+        <v>6859946</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620675</v>
+        <v>124620142</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,50 +1104,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481300</v>
+        <v>481241</v>
       </c>
       <c r="R6" t="n">
-        <v>6859946</v>
+        <v>6860052</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620934</v>
+        <v>124620046</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1236,20 +1227,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481353</v>
+        <v>481239</v>
       </c>
       <c r="R7" t="n">
-        <v>6859911</v>
+        <v>6860075</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124621255</v>
+        <v>124620597</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481309</v>
+        <v>481297</v>
       </c>
       <c r="R8" t="n">
-        <v>6859892</v>
+        <v>6859950</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124825238</v>
+        <v>124825237</v>
       </c>
       <c r="B9" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1451,13 +1451,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481211</v>
+        <v>481198</v>
       </c>
       <c r="R9" t="n">
-        <v>6859812</v>
+        <v>6859917</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1518,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124825237</v>
+        <v>124825238</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481198</v>
+        <v>481211</v>
       </c>
       <c r="R10" t="n">
-        <v>6859917</v>
+        <v>6859812</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124621053</v>
+        <v>124620934</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481346</v>
+        <v>481353</v>
       </c>
       <c r="R2" t="n">
-        <v>6859891</v>
+        <v>6859911</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124621255</v>
+        <v>124621053</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481309</v>
+        <v>481346</v>
       </c>
       <c r="R3" t="n">
-        <v>6859892</v>
+        <v>6859891</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124620934</v>
+        <v>124620046</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -912,20 +912,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481353</v>
+        <v>481239</v>
       </c>
       <c r="R4" t="n">
-        <v>6859911</v>
+        <v>6860075</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124620675</v>
+        <v>124620597</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1014,29 +1023,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481300</v>
+        <v>481297</v>
       </c>
       <c r="R5" t="n">
-        <v>6859946</v>
+        <v>6859950</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620142</v>
+        <v>124620675</v>
       </c>
       <c r="B6" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,41 +1104,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481241</v>
+        <v>481300</v>
       </c>
       <c r="R6" t="n">
-        <v>6860052</v>
+        <v>6859946</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620046</v>
+        <v>124621255</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1227,29 +1236,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481239</v>
+        <v>481309</v>
       </c>
       <c r="R7" t="n">
-        <v>6860075</v>
+        <v>6859892</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124620597</v>
+        <v>124620142</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,25 +1317,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481297</v>
+        <v>481241</v>
       </c>
       <c r="R8" t="n">
-        <v>6859950</v>
+        <v>6860052</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124620934</v>
+        <v>124620142</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481353</v>
+        <v>481241</v>
       </c>
       <c r="R2" t="n">
-        <v>6859911</v>
+        <v>6860052</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124621053</v>
+        <v>124620934</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481346</v>
+        <v>481353</v>
       </c>
       <c r="R3" t="n">
-        <v>6859891</v>
+        <v>6859911</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124620046</v>
+        <v>124621255</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -912,29 +912,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481239</v>
+        <v>481309</v>
       </c>
       <c r="R4" t="n">
-        <v>6860075</v>
+        <v>6859892</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124620597</v>
+        <v>124621053</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1030,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481297</v>
+        <v>481346</v>
       </c>
       <c r="R5" t="n">
-        <v>6859950</v>
+        <v>6859891</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620675</v>
+        <v>124620046</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1127,7 +1118,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1141,13 +1132,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481300</v>
+        <v>481239</v>
       </c>
       <c r="R6" t="n">
-        <v>6859946</v>
+        <v>6860075</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124621255</v>
+        <v>124620597</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1243,13 +1234,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481309</v>
+        <v>481297</v>
       </c>
       <c r="R7" t="n">
-        <v>6859892</v>
+        <v>6859950</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124620142</v>
+        <v>124620675</v>
       </c>
       <c r="B8" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,41 +1308,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481241</v>
+        <v>481300</v>
       </c>
       <c r="R8" t="n">
-        <v>6860052</v>
+        <v>6859946</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124620142</v>
+        <v>124620597</v>
       </c>
       <c r="B2" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481241</v>
+        <v>481297</v>
       </c>
       <c r="R2" t="n">
-        <v>6860052</v>
+        <v>6859950</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124620934</v>
+        <v>124620142</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481353</v>
+        <v>481241</v>
       </c>
       <c r="R3" t="n">
-        <v>6859911</v>
+        <v>6860052</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124621255</v>
+        <v>124621053</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481309</v>
+        <v>481346</v>
       </c>
       <c r="R4" t="n">
-        <v>6859892</v>
+        <v>6859891</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124621053</v>
+        <v>124620934</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481346</v>
+        <v>481353</v>
       </c>
       <c r="R5" t="n">
-        <v>6859891</v>
+        <v>6859911</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620597</v>
+        <v>124620675</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1227,20 +1227,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481297</v>
+        <v>481300</v>
       </c>
       <c r="R7" t="n">
-        <v>6859950</v>
+        <v>6859946</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124620675</v>
+        <v>124621255</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1329,29 +1338,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481300</v>
+        <v>481309</v>
       </c>
       <c r="R8" t="n">
-        <v>6859946</v>
+        <v>6859892</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124825237</v>
+        <v>124825238</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1451,13 +1451,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481198</v>
+        <v>481211</v>
       </c>
       <c r="R9" t="n">
-        <v>6859917</v>
+        <v>6859812</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1518,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124825238</v>
+        <v>124825237</v>
       </c>
       <c r="B10" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481211</v>
+        <v>481198</v>
       </c>
       <c r="R10" t="n">
-        <v>6859812</v>
+        <v>6859917</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124620597</v>
+        <v>124620675</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,20 +708,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481297</v>
+        <v>481300</v>
       </c>
       <c r="R2" t="n">
-        <v>6859950</v>
+        <v>6859946</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124620142</v>
+        <v>124620934</v>
       </c>
       <c r="B3" t="n">
-        <v>58191</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481241</v>
+        <v>481353</v>
       </c>
       <c r="R3" t="n">
-        <v>6860052</v>
+        <v>6859911</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124621053</v>
+        <v>124620597</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -919,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481346</v>
+        <v>481297</v>
       </c>
       <c r="R4" t="n">
-        <v>6859891</v>
+        <v>6859950</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124620934</v>
+        <v>124621255</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1021,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481353</v>
+        <v>481309</v>
       </c>
       <c r="R5" t="n">
-        <v>6859911</v>
+        <v>6859892</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620046</v>
+        <v>124621053</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1116,29 +1125,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481239</v>
+        <v>481346</v>
       </c>
       <c r="R6" t="n">
-        <v>6860075</v>
+        <v>6859891</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620675</v>
+        <v>124620142</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>58191</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,50 +1206,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481300</v>
+        <v>481241</v>
       </c>
       <c r="R7" t="n">
-        <v>6859946</v>
+        <v>6860052</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124621255</v>
+        <v>124620046</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1338,20 +1329,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481309</v>
+        <v>481239</v>
       </c>
       <c r="R8" t="n">
-        <v>6859892</v>
+        <v>6860075</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124620675</v>
+        <v>124620934</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,26 +708,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481300</v>
+        <v>481353</v>
       </c>
       <c r="R2" t="n">
-        <v>6859946</v>
+        <v>6859911</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124620934</v>
+        <v>124621255</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481353</v>
+        <v>481309</v>
       </c>
       <c r="R3" t="n">
-        <v>6859911</v>
+        <v>6859892</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124620597</v>
+        <v>124621053</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481297</v>
+        <v>481346</v>
       </c>
       <c r="R4" t="n">
-        <v>6859950</v>
+        <v>6859891</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124621255</v>
+        <v>124620046</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,20 +1014,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481309</v>
+        <v>481239</v>
       </c>
       <c r="R5" t="n">
-        <v>6859892</v>
+        <v>6860075</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124621053</v>
+        <v>124620675</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,17 +1125,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481346</v>
+        <v>481300</v>
       </c>
       <c r="R6" t="n">
-        <v>6859891</v>
+        <v>6859946</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620142</v>
+        <v>124620597</v>
       </c>
       <c r="B7" t="n">
-        <v>58191</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,13 +1243,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481241</v>
+        <v>481297</v>
       </c>
       <c r="R7" t="n">
-        <v>6860052</v>
+        <v>6859950</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124620046</v>
+        <v>124620142</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>58305</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,50 +1317,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481239</v>
+        <v>481241</v>
       </c>
       <c r="R8" t="n">
-        <v>6860075</v>
+        <v>6860052</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>124825238</v>
       </c>
       <c r="B9" t="n">
-        <v>78546</v>
+        <v>78683</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>124825237</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124825238</v>
+        <v>124825237</v>
       </c>
       <c r="B9" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1451,13 +1451,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481211</v>
+        <v>481198</v>
       </c>
       <c r="R9" t="n">
-        <v>6859812</v>
+        <v>6859917</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1518,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124825237</v>
+        <v>124825238</v>
       </c>
       <c r="B10" t="n">
-        <v>78684</v>
+        <v>78683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481198</v>
+        <v>481211</v>
       </c>
       <c r="R10" t="n">
-        <v>6859917</v>
+        <v>6859812</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1592,12 +1592,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1617,6 +1617,434 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126525136</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99374</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Acksjön, väg Ö om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>481265</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6859305</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>vägkant, dike, kärr</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johanne Maad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johanne Maad, Staffan Jansson, Kerstin Vikman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126525145</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98265</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Acksjön, väg Ö om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>481265</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6859305</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>vägkant, dike, kärr</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johanne Maad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johanne Maad, Staffan Jansson, Kerstin Vikman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126525181</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98278</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Acksjön, väg Ö om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>481265</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6859305</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>vägkant, dike, kärr</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johanne Maad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Johanne Maad, Staffan Jansson, Kerstin Vikman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126525188</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97242</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Acksjön, väg Ö om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>481265</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6859305</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>vägkant, dike, kärr</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johanne Maad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Johanne Maad, Staffan Jansson, Kerstin Vikman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124620934</v>
+        <v>124825238</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
+          <t>Kropptjärn, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481353</v>
+        <v>481211</v>
       </c>
       <c r="R2" t="n">
-        <v>6859911</v>
+        <v>6859812</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,49 +769,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124621255</v>
+        <v>124620142</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +816,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481309</v>
+        <v>481241</v>
       </c>
       <c r="R3" t="n">
-        <v>6859892</v>
+        <v>6860052</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,53 +878,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124621053</v>
+        <v>126525181</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
+          <t>Acksjön, väg Ö om, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481346</v>
+        <v>481265</v>
       </c>
       <c r="R4" t="n">
-        <v>6859891</v>
+        <v>6859305</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,80 +961,76 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>vägkant, dike, kärr</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Johanne Maad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Johanne Maad, Staffan Jansson, Kerstin Vikman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124620046</v>
+        <v>126525145</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
+          <t>Acksjön, väg Ö om, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481239</v>
+        <v>481265</v>
       </c>
       <c r="R5" t="n">
-        <v>6860075</v>
+        <v>6859305</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,12 +1054,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1074,33 +1068,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>vägkant, dike, kärr</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Johanne Maad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Johanne Maad, Staffan Jansson, Kerstin Vikman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124620675</v>
+        <v>124620046</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,7 +1122,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1141,13 +1136,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481300</v>
+        <v>481239</v>
       </c>
       <c r="R6" t="n">
-        <v>6859946</v>
+        <v>6860075</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,15 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124620597</v>
+        <v>124620167</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,13 +1233,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481297</v>
+        <v>481238</v>
       </c>
       <c r="R7" t="n">
-        <v>6859950</v>
+        <v>6860046</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,37 +1295,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124620142</v>
+        <v>124620597</v>
       </c>
       <c r="B8" t="n">
-        <v>58305</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,13 +1330,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481241</v>
+        <v>481297</v>
       </c>
       <c r="R8" t="n">
-        <v>6860052</v>
+        <v>6859950</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,52 +1392,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124825238</v>
+        <v>124620675</v>
       </c>
       <c r="B9" t="n">
-        <v>78683</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kropptjärn, Dlr</t>
+          <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481211</v>
+        <v>481300</v>
       </c>
       <c r="R9" t="n">
-        <v>6859812</v>
+        <v>6859946</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1476,17 +1466,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,64 +1486,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124825237</v>
+        <v>124620934</v>
       </c>
       <c r="B10" t="n">
-        <v>78684</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kropptjärn, Dlr</t>
+          <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481198</v>
+        <v>481353</v>
       </c>
       <c r="R10" t="n">
-        <v>6859917</v>
+        <v>6859911</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,17 +1563,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,64 +1583,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126525136</v>
+        <v>124621053</v>
       </c>
       <c r="B11" t="n">
-        <v>99374</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222467</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hoppe</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Acksjön, väg Ö om, Dlr</t>
+          <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481265</v>
+        <v>481346</v>
       </c>
       <c r="R11" t="n">
-        <v>6859305</v>
+        <v>6859891</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1688,12 +1660,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1702,76 +1674,66 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>vägkant, dike, kärr</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johanne Maad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johanne Maad, Staffan Jansson, Kerstin Vikman</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126525145</v>
+        <v>124621255</v>
       </c>
       <c r="B12" t="n">
-        <v>98265</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Acksjön, väg Ö om, Dlr</t>
+          <t>Stora Acksjöberget, Stora Acksjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481265</v>
+        <v>481309</v>
       </c>
       <c r="R12" t="n">
-        <v>6859305</v>
+        <v>6859892</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,12 +1757,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,34 +1771,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>vägkant, dike, kärr</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johanne Maad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johanne Maad, Staffan Jansson, Kerstin Vikman</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126525181</v>
+        <v>126525188</v>
       </c>
       <c r="B13" t="n">
-        <v>98278</v>
+        <v>97986</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,21 +1800,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>221946</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1940,10 +1896,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126525188</v>
+        <v>126525136</v>
       </c>
       <c r="B14" t="n">
-        <v>97242</v>
+        <v>100143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,21 +1907,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221946</v>
+        <v>222467</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2045,6 +2001,112 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124825237</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kropptjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>481198</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6859917</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20596-2025 artfynd.xlsx
+++ b/artfynd/A 20596-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825238</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124620142</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126525181</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126525145</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124620046</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124620167</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124620597</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124620675</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124620934</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1689,6 +1739,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124621053</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1786,6 +1841,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124621255</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126525188</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2000,6 +2065,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126525136</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2106,8 +2176,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825237</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>